--- a/measurements/28/Filled_2D_sections/sagittal/week28_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/sagittal/week28_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,82 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +576,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.758477096966092</v>
+        <v>1813.832199546485</v>
       </c>
       <c r="D2" t="n">
-        <v>9.357237769336235</v>
+        <v>182.688927877517</v>
       </c>
       <c r="E2" t="n">
-        <v>8.837391225303092</v>
+        <v>172.5395429702032</v>
       </c>
       <c r="F2" t="n">
         <v>1.05882352956659</v>
@@ -525,15 +595,42 @@
         <v>0.6829399479365479</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.719122023809524</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.904761904761904</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.811941964285714</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.904761904761904</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.719122023809524</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.803331350386675</v>
+      <c r="AC2" s="2" t="n">
+        <v>2212.108843537415</v>
       </c>
     </row>
     <row r="3">
@@ -544,17 +641,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.73081499107674</v>
+        <v>2184.467120181406</v>
       </c>
       <c r="D3" t="n">
-        <v>12.62020717016081</v>
+        <v>246.3945209412348</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64675136310298</v>
+        <v>207.865145660582</v>
       </c>
       <c r="F3" t="n">
         <v>1.185357555535387</v>
@@ -566,21 +663,39 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6851181402439025</v>
+        <v>13.37611607142857</v>
       </c>
       <c r="J3" t="n">
-        <v>0.784203506097561</v>
+        <v>15.31063988095238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7346608231707317</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>14.34337797619047</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.31063988095238</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.37611607142857</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>11.19322411272584</v>
+      <c r="AC3" s="2" t="n">
+        <v>218.5343755341711</v>
       </c>
     </row>
     <row r="4">
@@ -591,20 +706,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.782272456870911</v>
+        <v>2204.081632653061</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43590595664048</v>
+        <v>242.7962591534569</v>
       </c>
       <c r="E4" t="n">
-        <v>10.66103887267229</v>
+        <v>208.1440922759828</v>
       </c>
       <c r="F4" t="n">
-        <v>1.166481625774552</v>
+        <v>1.166481625774553</v>
       </c>
       <c r="G4" t="n">
         <v>0.4698438615469742</v>
@@ -613,21 +728,39 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6134717987804879</v>
+        <v>11.97730654761905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7725800304878049</v>
+        <v>15.08370535714286</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6930259146341464</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>13.53050595238095</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15.08370535714286</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11.97730654761905</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.38166648556546</v>
+      <c r="AC4" s="2" t="n">
+        <v>202.6896790038972</v>
       </c>
     </row>
     <row r="5">
@@ -638,42 +771,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.815883402736467</v>
+        <v>2216.893424036281</v>
       </c>
       <c r="D5" t="n">
-        <v>12.57142665618803</v>
+        <v>245.4421394779569</v>
       </c>
       <c r="E5" t="n">
-        <v>10.66103885231949</v>
+        <v>208.1440918786185</v>
       </c>
       <c r="F5" t="n">
         <v>1.179193400411716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4624410975349486</v>
+        <v>0.4624410975349484</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5960365853658537</v>
+        <v>5.094866071428571</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7727705792682927</v>
+        <v>15.08742559523809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6844035823170732</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>10.60639880952381</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15.08742559523809</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11.63690476190476</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.094866071428571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AC5" s="2" t="n">
         <v>1.077006766396628</v>
       </c>
     </row>
@@ -685,43 +839,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.869125520523498</v>
+        <v>2237.18820861678</v>
       </c>
       <c r="D6" t="n">
-        <v>12.35018112019795</v>
+        <v>241.1225837752932</v>
       </c>
       <c r="E6" t="n">
-        <v>10.79901092226912</v>
+        <v>210.837832291921</v>
       </c>
       <c r="F6" t="n">
         <v>1.143640024914697</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4835446785782056</v>
+        <v>0.4835446785782057</v>
       </c>
       <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.456473214285714</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.12351190476191</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.58655753968254</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.8258384146341464</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8258384146341464</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.8258384146341464</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>16.12351190476191</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9.1796875</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.456473214285714</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.5916661486435019</v>
+      <c r="AC6" s="2" t="n">
+        <v>0.591666148643502</v>
       </c>
     </row>
     <row r="7">
@@ -732,17 +907,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.924152290303391</v>
+        <v>2258.163265306122</v>
       </c>
       <c r="D7" t="n">
-        <v>11.88156642274159</v>
+        <v>231.9734396820976</v>
       </c>
       <c r="E7" t="n">
-        <v>10.86799696305903</v>
+        <v>212.1847026121049</v>
       </c>
       <c r="F7" t="n">
         <v>1.093261846053853</v>
@@ -751,24 +926,45 @@
         <v>0.5273375265429292</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.680059523809524</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16.38764880952381</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.388640873015873</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.8393673780487805</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8393673780487805</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8393673780487805</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>16.38764880952381</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.098214285714286</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.680059523809524</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.55</v>
+      <c r="AC7" s="2" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="8">
@@ -779,17 +975,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.946757882212969</v>
+        <v>2266.780045351474</v>
       </c>
       <c r="D8" t="n">
-        <v>11.91014134302372</v>
+        <v>232.531330982844</v>
       </c>
       <c r="E8" t="n">
-        <v>10.89065380503492</v>
+        <v>212.6270504792531</v>
       </c>
       <c r="F8" t="n">
         <v>1.093611233654078</v>
@@ -798,24 +994,48 @@
         <v>0.5268127653654884</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.391369047619047</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16.11979166666666</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.030784970238094</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.8256478658536586</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.8256478658536586</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.8256478658536586</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>16.11979166666666</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.65438988095238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.957589285714286</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.391369047619047</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7335056211890244</v>
+      <c r="AC8" s="2" t="n">
+        <v>3.563151041666667</v>
       </c>
     </row>
     <row r="9">
@@ -826,43 +1046,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.972040452111838</v>
+        <v>2276.417233560091</v>
       </c>
       <c r="D9" t="n">
-        <v>11.78155407382221</v>
+        <v>230.0208176317669</v>
       </c>
       <c r="E9" t="n">
-        <v>10.90494128262124</v>
+        <v>212.9059964702243</v>
       </c>
       <c r="F9" t="n">
         <v>1.080386750233858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5406639874739569</v>
+        <v>0.5406639874739571</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.510416666666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.94977678571428</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.597842261904762</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.7657202743902439</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7657202743902439</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7657202743902439</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>14.94977678571428</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.710193452380952</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.220982142857143</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.510416666666667</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7878715701219512</v>
+      <c r="AC9" s="2" t="n">
+        <v>10.35621279761905</v>
       </c>
     </row>
     <row r="10">
@@ -873,43 +1117,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.046103509815587</v>
+        <v>2304.648526077097</v>
       </c>
       <c r="D10" t="n">
-        <v>12.48223510021117</v>
+        <v>243.7007805279323</v>
       </c>
       <c r="E10" t="n">
-        <v>10.7241068380635</v>
+        <v>209.3754192193349</v>
       </c>
       <c r="F10" t="n">
         <v>1.163941695909582</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4876415755171342</v>
+        <v>0.4876415755171341</v>
       </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.627604166666667</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13.99553571428571</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.312779017857142</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.716844512195122</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.716844512195122</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.716844512195122</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>13.99553571428571</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.738095238095237</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.889880952380952</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.627604166666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7606885956554879</v>
+      <c r="AC10" s="2" t="n">
+        <v>6.618625992063491</v>
       </c>
     </row>
     <row r="11">
@@ -920,26 +1188,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.125223081499108</v>
+        <v>2334.807256235827</v>
       </c>
       <c r="D11" t="n">
-        <v>11.08924251358684</v>
+        <v>216.5042585986001</v>
       </c>
       <c r="E11" t="n">
-        <v>10.68961383366003</v>
+        <v>208.7019843714578</v>
       </c>
       <c r="F11" t="n">
         <v>1.037384763018139</v>
       </c>
       <c r="G11" t="n">
-        <v>0.625933235112376</v>
+        <v>0.6259332351123761</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.290922619047619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.93257068452381</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.0078125</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.336309523809524</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.290922619047619</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="12">
@@ -950,26 +1259,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.068411659726354</v>
+        <v>2313.151927437641</v>
       </c>
       <c r="D12" t="n">
-        <v>10.92514682979118</v>
+        <v>213.3004857244946</v>
       </c>
       <c r="E12" t="n">
-        <v>10.58021670434533</v>
+        <v>206.566135656266</v>
       </c>
       <c r="F12" t="n">
         <v>1.032601423494869</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6388962415148683</v>
+        <v>0.6388962415148682</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.963169642857143</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.18563988095238</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.713665674603174</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.18563988095238</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.9921875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.963169642857143</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>15.38225446428571</v>
       </c>
     </row>
     <row r="13">
@@ -980,26 +1327,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.019928613920285</v>
+        <v>2294.671201814059</v>
       </c>
       <c r="D13" t="n">
-        <v>10.80146226068822</v>
+        <v>210.8856917562939</v>
       </c>
       <c r="E13" t="n">
-        <v>10.49694320341436</v>
+        <v>204.9403196857089</v>
       </c>
       <c r="F13" t="n">
-        <v>1.029010260546595</v>
+        <v>1.029010260546596</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6483896893813679</v>
+        <v>0.648389689381368</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.894345238095238</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.271205357142857</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.558655753968253</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.271205357142857</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6.510416666666666</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.894345238095238</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>12.33010912698413</v>
       </c>
     </row>
     <row r="14">
@@ -1010,26 +1395,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.970850684116598</v>
+        <v>2275.963718820862</v>
       </c>
       <c r="D14" t="n">
-        <v>10.76696924756213</v>
+        <v>210.2122567381178</v>
       </c>
       <c r="E14" t="n">
-        <v>10.42203912793136</v>
+        <v>203.4779067834218</v>
       </c>
       <c r="F14" t="n">
         <v>1.033096221900218</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6472307306292713</v>
+        <v>0.6472307306292714</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.307291666666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.919642857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.569816468253968</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6.919642857142857</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.48251488095238</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.307291666666667</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
@@ -1040,17 +1463,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.915229030339084</v>
+        <v>2254.761904761905</v>
       </c>
       <c r="D15" t="n">
-        <v>10.63491525301119</v>
+        <v>207.6340597016471</v>
       </c>
       <c r="E15" t="n">
-        <v>10.35897114509489</v>
+        <v>202.2465794994717</v>
       </c>
       <c r="F15" t="n">
         <v>1.026638177098018</v>
@@ -1059,7 +1482,45 @@
         <v>0.6572239204535681</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.165922619047619</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.899181547619047</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.435267857142858</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.899181547619047</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.240699404761904</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.165922619047619</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>7.141203703703703</v>
       </c>
     </row>
     <row r="16">
@@ -1070,26 +1531,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.854550862581797</v>
+        <v>2231.632653061224</v>
       </c>
       <c r="D16" t="n">
-        <v>10.5540930759616</v>
+        <v>206.0561029116313</v>
       </c>
       <c r="E16" t="n">
-        <v>10.24957404485563</v>
+        <v>200.1107313519432</v>
       </c>
       <c r="F16" t="n">
         <v>1.029710408429979</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6604829448550178</v>
+        <v>0.6604829448550177</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.056547619047619</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.83407738095238</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.274553571428572</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.83407738095238</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.788690476190476</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.418898809523809</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.056547619047619</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>5.449883078231292</v>
       </c>
     </row>
     <row r="17">
@@ -1100,26 +1602,67 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.798036882807852</v>
+        <v>2210.090702947846</v>
       </c>
       <c r="D17" t="n">
-        <v>10.47673765624442</v>
+        <v>204.5458304314386</v>
       </c>
       <c r="E17" t="n">
-        <v>10.19242416940084</v>
+        <v>198.9949480692545</v>
       </c>
       <c r="F17" t="n">
-        <v>1.027894589365415</v>
+        <v>1.027894589365416</v>
       </c>
       <c r="G17" t="n">
         <v>0.6638022186002521</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.11235119047619</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.787574404761904</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.036923363095238</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.787574404761904</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.8828125</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.364955357142857</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11235119047619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>3.502604166666667</v>
       </c>
     </row>
     <row r="18">
@@ -1130,17 +1673,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.726650803093397</v>
+        <v>2182.879818594104</v>
       </c>
       <c r="D18" t="n">
-        <v>10.39938221326688</v>
+        <v>203.0355574971153</v>
       </c>
       <c r="E18" t="n">
-        <v>10.05445208782103</v>
+        <v>196.3012074288868</v>
       </c>
       <c r="F18" t="n">
         <v>1.034306208079073</v>
@@ -1149,7 +1692,51 @@
         <v>0.6654194409450671</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.588541666666666</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.392485119047619</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.588541666666666</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.406622023809524</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.484002976190476</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.177455357142857</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -1160,26 +1747,70 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.656454491374182</v>
+        <v>2156.122448979592</v>
       </c>
       <c r="D19" t="n">
-        <v>10.34713502337293</v>
+        <v>202.0154933134715</v>
       </c>
       <c r="E19" t="n">
-        <v>9.973629951477051</v>
+        <v>194.7232514335996</v>
       </c>
       <c r="F19" t="n">
-        <v>1.037449261072752</v>
+        <v>1.037449261072751</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6639172132226574</v>
+        <v>0.6639172132226575</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.199776785714286</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.605282738095238</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.377976190476191</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.605282738095238</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.859747023809524</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.521205357142857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.199776785714286</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>2.627418154761905</v>
       </c>
     </row>
     <row r="20">
@@ -1190,26 +1821,70 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.586555621653778</v>
+        <v>2129.478458049886</v>
       </c>
       <c r="D20" t="n">
-        <v>10.26386151662687</v>
+        <v>200.3896772293817</v>
       </c>
       <c r="E20" t="n">
-        <v>9.876068978774839</v>
+        <v>192.818489585604</v>
       </c>
       <c r="F20" t="n">
         <v>1.039265879844041</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6663960644794958</v>
+        <v>0.6663960644794957</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.681547619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.922247023809524</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.681547619047619</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.617931547619047</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.035714285714286</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.808500744047619</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>1.295805431547619</v>
       </c>
     </row>
     <row r="21">
@@ -1220,26 +1895,70 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.49910767400357</v>
+        <v>2096.145124716553</v>
       </c>
       <c r="D21" t="n">
-        <v>10.21508105208234</v>
+        <v>199.4372967311314</v>
       </c>
       <c r="E21" t="n">
-        <v>9.746466340088263</v>
+        <v>190.2881523541042</v>
       </c>
       <c r="F21" t="n">
         <v>1.048080473029144</v>
       </c>
       <c r="G21" t="n">
-        <v>0.662244642472566</v>
+        <v>0.6622446424725662</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.140252976190476</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.293526785714286</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.949528769841269</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.293526785714286</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.653273809523809</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.140252976190476</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.581845238095238</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.687593005952381</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>1.130952380952381</v>
       </c>
     </row>
     <row r="22">
@@ -1249,7 +1968,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>2.808779761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1263,6 +1990,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>1.748046875</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1272,6 +2007,46 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/28/Filled_2D_sections/sagittal/week28_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/sagittal/week28_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2052,4 +2258,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week28_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2212.108843537415</v>
+      </c>
+      <c r="D10" t="n">
+        <v>112.5169158861548</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1813.832199546485</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2334.807256235827</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>218.5343755341711</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19.00454394801857</v>
+      </c>
+      <c r="E11" t="n">
+        <v>182.688927877517</v>
+      </c>
+      <c r="F11" t="n">
+        <v>246.3945209412348</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.077006766396628</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05789106775127008</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.026638177098018</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.185357555535387</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.591666148643502</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08521235778367871</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4521611907073455</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6829399479365479</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.182103388478619</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8013147091860318</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.231174022502185</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.54985119047619</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.625407957046477</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.63690476190476</v>
+      </c>
+      <c r="F48" t="n">
+        <v>16.38764880952381</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>34</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.230742296918767</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.500362669470128</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.484002976190476</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.1796875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>28</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.99570843962585</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.8255038192898713</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.056547619047619</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.418898809523809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>